--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2026 artfynd.xlsx
+++ b/artfynd/A 32097-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579793</v>
       </c>
       <c r="B2" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
